--- a/data/trans_dic/P1421-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1421-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,95</t>
+          <t>1,61; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,68</t>
+          <t>0,61; 4,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,93</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,32</t>
+          <t>1,69; 5,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,2</t>
+          <t>2,55; 8,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,2</t>
+          <t>5,18; 12,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,41</t>
+          <t>6,07; 13,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 14,16</t>
+          <t>8,47; 14,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,2</t>
+          <t>2,5; 5,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,9</t>
+          <t>3,16; 7,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,24</t>
+          <t>3,3; 7,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,39</t>
+          <t>5,73; 9,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,93</t>
+          <t>0,22; 2,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,73</t>
+          <t>0,21; 2,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,71</t>
+          <t>0,17; 1,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 9,72</t>
+          <t>4,57; 10,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,22</t>
+          <t>6,26; 11,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,13</t>
+          <t>3,14; 6,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,4</t>
+          <t>2,04; 5,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 17,13</t>
+          <t>11,06; 16,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,36</t>
+          <t>3,63; 6,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,19</t>
+          <t>1,95; 4,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,95</t>
+          <t>1,31; 3,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,55</t>
+          <t>8,64; 12,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,86</t>
+          <t>0,85; 4,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,23</t>
+          <t>0,57; 3,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,64</t>
+          <t>2,86; 7,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,62</t>
+          <t>2,4; 7,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,66</t>
+          <t>2,26; 6,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,55</t>
+          <t>1,96; 6,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 15,91</t>
+          <t>10,0; 15,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,69</t>
+          <t>1,94; 4,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,26</t>
+          <t>1,73; 4,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,47</t>
+          <t>1,16; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,69</t>
+          <t>7,19; 11,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,82</t>
+          <t>0,68; 3,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,42</t>
+          <t>0,55; 3,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,67</t>
+          <t>0,82; 3,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,6</t>
+          <t>0,91; 4,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,74</t>
+          <t>2,54; 6,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,66</t>
+          <t>6,17; 12,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,96</t>
+          <t>5,03; 11,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,29</t>
+          <t>5,22; 9,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,41</t>
+          <t>1,99; 4,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,3</t>
+          <t>3,97; 7,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,61</t>
+          <t>3,21; 6,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,38</t>
+          <t>3,42; 5,9</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,73</t>
+          <t>0,44; 3,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,82</t>
+          <t>0,88; 4,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,94</t>
+          <t>2,92; 8,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,64</t>
+          <t>1,12; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,29</t>
+          <t>6,48; 14,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 13,31</t>
+          <t>5,76; 13,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 15,93</t>
+          <t>8,87; 14,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,87</t>
+          <t>1,11; 3,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,11</t>
+          <t>3,65; 8,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,29</t>
+          <t>3,7; 7,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,37</t>
+          <t>6,69; 10,68</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,33</t>
+          <t>1,67; 6,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,34</t>
+          <t>0,67; 4,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,87</t>
+          <t>0,8; 4,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,11</t>
+          <t>4,26; 9,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,41</t>
+          <t>3,57; 9,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,63</t>
+          <t>2,81; 7,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,47</t>
+          <t>3,46; 9,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 18,38</t>
+          <t>11,54; 18,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,98</t>
+          <t>3,23; 7,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,9</t>
+          <t>1,98; 4,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,03</t>
+          <t>2,62; 6,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,4; 12,8</t>
+          <t>8,54; 12,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,11</t>
+          <t>0,96; 3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,56</t>
+          <t>0,62; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,68</t>
+          <t>1,26; 3,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,54</t>
+          <t>5,23; 9,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,74</t>
+          <t>2,61; 5,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,41</t>
+          <t>2,92; 6,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,84</t>
+          <t>4,11; 7,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,02</t>
+          <t>14,41; 19,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,96</t>
+          <t>2,02; 3,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,95</t>
+          <t>2,09; 4,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,37</t>
+          <t>3,05; 5,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 13,04</t>
+          <t>10,63; 14,25</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,72</t>
+          <t>2,74; 5,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,29</t>
+          <t>0,13; 1,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,16</t>
+          <t>0,59; 2,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,95</t>
+          <t>0,72; 2,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,78</t>
+          <t>6,1; 9,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,42</t>
+          <t>2,08; 4,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,8</t>
+          <t>2,79; 5,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,34</t>
+          <t>3,92; 6,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,21</t>
+          <t>4,81; 7,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,66</t>
+          <t>1,26; 2,72</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,57</t>
+          <t>1,86; 3,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,58</t>
+          <t>2,53; 4,27</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,0</t>
+          <t>1,95; 3,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,63</t>
+          <t>0,88; 1,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,85</t>
+          <t>1,05; 1,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,28</t>
+          <t>3,78; 5,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,65</t>
+          <t>4,98; 6,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,13</t>
+          <t>4,57; 6,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,37</t>
+          <t>4,69; 6,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,89; 11,77</t>
+          <t>10,44; 12,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,59</t>
+          <t>3,64; 4,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,77</t>
+          <t>2,89; 3,77</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,04</t>
+          <t>3,06; 3,95</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,41</t>
+          <t>7,51; 8,66</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43632</t>
+          <t>46178</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4043; 16238</t>
+          <t>4400; 16260</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1791; 10845</t>
+          <t>1801; 12269</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>970; 8621</t>
+          <t>951; 8328</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6070; 22808</t>
+          <t>5390; 18826</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6314; 21376</t>
+          <t>6643; 22504</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14549; 35058</t>
+          <t>14866; 35144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17278; 38711</t>
+          <t>17531; 37791</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24776; 41001</t>
+          <t>26756; 45557</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13493; 33087</t>
+          <t>13349; 31715</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19422; 40179</t>
+          <t>18411; 42606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18830; 42159</t>
+          <t>19226; 42215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33500; 56450</t>
+          <t>36373; 59587</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>36041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>75963</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>106698</t>
+          <t>112004</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1045; 9517</t>
+          <t>1067; 10005</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1898; 13804</t>
+          <t>1044; 13917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>862; 8571</t>
+          <t>854; 7400</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21960; 50278</t>
+          <t>24208; 53280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31859; 56530</t>
+          <t>31557; 57525</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16221; 37354</t>
+          <t>16438; 36278</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10944; 28266</t>
+          <t>10686; 27608</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58061; 87974</t>
+          <t>60287; 91551</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37760; 63435</t>
+          <t>36183; 63923</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20619; 43169</t>
+          <t>20056; 43298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12985; 30276</t>
+          <t>13457; 30944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88362; 129406</t>
+          <t>92854; 135874</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>44616</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57735</t>
+          <t>59689</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2791; 15486</t>
+          <t>2701; 13307</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1865; 10454</t>
+          <t>1849; 10390</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5587</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8854; 24124</t>
+          <t>8985; 23525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8025; 22195</t>
+          <t>8046; 23962</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7327; 22702</t>
+          <t>7724; 22840</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6830; 22030</t>
+          <t>6606; 21184</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33182; 55563</t>
+          <t>35635; 55860</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12506; 30704</t>
+          <t>12678; 30406</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11308; 28322</t>
+          <t>11493; 27763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7251; 22712</t>
+          <t>7621; 22557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46301; 71109</t>
+          <t>48218; 74653</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>28855</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>36253</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2682; 13684</t>
+          <t>2447; 14301</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2815; 12809</t>
+          <t>2067; 13102</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3043; 13589</t>
+          <t>3028; 12949</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3733; 14379</t>
+          <t>3383; 16833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8922; 25053</t>
+          <t>9423; 24493</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25652; 49243</t>
+          <t>24011; 47393</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19051; 42439</t>
+          <t>19484; 42881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14964; 34657</t>
+          <t>22038; 39127</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14003; 32234</t>
+          <t>14498; 33400</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30093; 55686</t>
+          <t>30295; 56029</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25476; 50021</t>
+          <t>24290; 50634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21491; 42382</t>
+          <t>27209; 46882</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>36475</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>916; 7579</t>
+          <t>904; 7412</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7704</t>
+          <t>0; 6777</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1837; 10174</t>
+          <t>1854; 10464</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5505; 15988</t>
+          <t>6005; 16721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2224; 13795</t>
+          <t>2333; 12361</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13612; 31384</t>
+          <t>14227; 32756</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11732; 29085</t>
+          <t>12582; 28672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20009; 33180</t>
+          <t>20116; 33408</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4027; 15904</t>
+          <t>4569; 16329</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15992; 35066</t>
+          <t>15780; 36808</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15530; 35641</t>
+          <t>15900; 34119</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27867; 43994</t>
+          <t>28923; 46196</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>38641</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54814</t>
+          <t>55599</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4594; 17153</t>
+          <t>4515; 17599</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1931; 11887</t>
+          <t>1837; 12363</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2040; 12806</t>
+          <t>2115; 12945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11347; 24568</t>
+          <t>11540; 24452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10130; 26170</t>
+          <t>9921; 25715</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6950; 21224</t>
+          <t>7801; 21829</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9403; 25870</t>
+          <t>9440; 25570</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>29224; 47131</t>
+          <t>30349; 48246</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17758; 38293</t>
+          <t>17742; 38496</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11599; 27049</t>
+          <t>10909; 26986</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12806; 32342</t>
+          <t>14066; 33250</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44185; 67313</t>
+          <t>45602; 67763</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47641</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>109286</t>
+          <t>129461</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>156927</t>
+          <t>182445</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5445; 19110</t>
+          <t>5912; 20133</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4291; 16964</t>
+          <t>4110; 16861</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8768; 24189</t>
+          <t>8280; 24393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33343; 65643</t>
+          <t>37539; 71572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16503; 36623</t>
+          <t>16653; 37160</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20769; 44510</t>
+          <t>20294; 44219</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28465; 54224</t>
+          <t>28409; 54184</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>52813; 152683</t>
+          <t>110827; 149234</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25638; 49619</t>
+          <t>25322; 48860</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29333; 53531</t>
+          <t>28351; 54400</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41271; 72410</t>
+          <t>41128; 72262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97102; 191601</t>
+          <t>158059; 211854</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>42323</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51971</t>
+          <t>54075</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19221; 42579</t>
+          <t>20367; 41240</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1013; 10059</t>
+          <t>1027; 9897</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4615; 16779</t>
+          <t>4562; 16949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3179; 18139</t>
+          <t>5728; 19646</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>47321; 76650</t>
+          <t>47792; 76524</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16657; 36326</t>
+          <t>17109; 37718</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21676; 47925</t>
+          <t>23027; 46707</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>31238; 59678</t>
+          <t>32565; 54617</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>72048; 110048</t>
+          <t>73426; 110354</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20526; 42531</t>
+          <t>20242; 43584</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30469; 57325</t>
+          <t>29848; 56797</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32189; 75235</t>
+          <t>41255; 69500</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>582717</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>62800; 98230</t>
+          <t>63733; 98843</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30012; 55803</t>
+          <t>30091; 56183</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35392; 62858</t>
+          <t>35615; 64238</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>115766; 182537</t>
+          <t>133411; 188991</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>170511; 224671</t>
+          <t>168324; 222270</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>166549; 217776</t>
+          <t>162510; 218997</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>169038; 225855</t>
+          <t>166148; 223414</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>325032; 430155</t>
+          <t>389366; 457124</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>243028; 305286</t>
+          <t>241953; 304359</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>202730; 263268</t>
+          <t>201953; 262877</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>211957; 280336</t>
+          <t>212211; 273862</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>470235; 597952</t>
+          <t>545152; 628725</t>
         </is>
       </c>
     </row>
